--- a/research/traditional_assets/database/data/croatia/croatia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0626</v>
+        <v>0.062</v>
       </c>
       <c r="E2">
-        <v>0.07969999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>230.88</v>
+        <v>418.22</v>
       </c>
       <c r="L2">
-        <v>0.2866650111745717</v>
+        <v>0.5216013968570716</v>
       </c>
       <c r="M2">
-        <v>1.9542</v>
+        <v>264.68</v>
       </c>
       <c r="N2">
-        <v>0.000562796993347349</v>
+        <v>0.08297438791184676</v>
       </c>
       <c r="O2">
-        <v>0.008464137214137213</v>
+        <v>0.6328726507579743</v>
       </c>
       <c r="P2">
-        <v>1.8352</v>
+        <v>264.68</v>
       </c>
       <c r="Q2">
-        <v>0.0005285257610229531</v>
+        <v>0.08297438791184676</v>
       </c>
       <c r="R2">
-        <v>0.007948717948717949</v>
+        <v>0.6328726507579743</v>
       </c>
       <c r="S2">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.06089448367618463</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1154.5</v>
+        <v>1050.8</v>
       </c>
       <c r="V2">
-        <v>0.3324885522564294</v>
+        <v>0.3294147151948337</v>
       </c>
       <c r="W2">
-        <v>0.09640003654071831</v>
+        <v>0.1025974025974026</v>
       </c>
       <c r="X2">
-        <v>0.05397836608880691</v>
+        <v>0.07959923857111041</v>
       </c>
       <c r="Y2">
-        <v>0.04242167045191141</v>
+        <v>0.02299816402629219</v>
       </c>
       <c r="Z2">
-        <v>0.3155337904015671</v>
+        <v>0.2937964896852442</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05362797311671863</v>
+        <v>0.07958992383994333</v>
       </c>
       <c r="AC2">
-        <v>-0.05362797311671863</v>
+        <v>-0.07958992383994333</v>
       </c>
       <c r="AD2">
-        <v>139.9</v>
+        <v>372.701</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>139.9</v>
+        <v>372.701</v>
       </c>
       <c r="AG2">
-        <v>-1014.6</v>
+        <v>-678.0989999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03872985991916283</v>
+        <v>0.1046148586383937</v>
       </c>
       <c r="AI2">
-        <v>0.0353051027103417</v>
+        <v>0.1070579648240701</v>
       </c>
       <c r="AJ2">
-        <v>-0.4128249989827887</v>
+        <v>-0.2699652560055513</v>
       </c>
       <c r="AK2">
-        <v>-0.3613119190912005</v>
+        <v>-0.2789955651118843</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hrvatska postanska banka d.d. (ZGSE:HPB)</t>
+          <t>Istarska kreditna banka Umag d.d. (ZGSE:IKBA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04190000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="E3">
-        <v>0.0643</v>
+        <v>0.172</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,58 +728,61 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>34.7</v>
+        <v>6.32</v>
       </c>
       <c r="L3">
-        <v>0.2780448717948718</v>
+        <v>0.3550561797752809</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.08</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06209677419354839</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4873417721518987</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.08</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06209677419354839</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4873417721518987</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>255.6</v>
+        <v>26.2</v>
       </c>
       <c r="V3">
-        <v>1.14876404494382</v>
+        <v>0.5282258064516129</v>
       </c>
       <c r="W3">
-        <v>0.09119579500657031</v>
+        <v>0.1025974025974026</v>
       </c>
       <c r="X3">
-        <v>0.05334437448743433</v>
+        <v>0.07958488326285784</v>
       </c>
       <c r="Y3">
-        <v>0.03785142051913598</v>
+        <v>0.02301251933454476</v>
       </c>
       <c r="Z3">
-        <v>0.593437945791726</v>
+        <v>0.6116838487972509</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05334437448743433</v>
+        <v>0.07958488326285784</v>
       </c>
       <c r="AC3">
-        <v>-0.05334437448743433</v>
+        <v>-0.07958488326285784</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-255.6</v>
+        <v>-26.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>7.722054380664654</v>
+        <v>-1.119658119658119</v>
       </c>
       <c r="AK3">
-        <v>-1.608558842039018</v>
+        <v>-0.9128919860627178</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Istarska kreditna banka Umag d.d. (ZGSE:IKBA)</t>
+          <t>Hrvatska postanska banka d.d. (ZGSE:HPB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.148</v>
+        <v>0.0917</v>
       </c>
       <c r="E4">
-        <v>0.0951</v>
+        <v>0.982</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,85 +850,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>5.7</v>
+        <v>145.8</v>
       </c>
       <c r="L4">
-        <v>0.3097826086956522</v>
+        <v>1.442136498516321</v>
       </c>
       <c r="M4">
-        <v>1.9542</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04641805225653206</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3428421052631579</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>1.8352</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04359144893111638</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.3219649122807017</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.119</v>
-      </c>
-      <c r="T4">
-        <v>0.06089448367618463</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>32.5</v>
+        <v>241.9</v>
       </c>
       <c r="V4">
-        <v>0.7719714964370546</v>
+        <v>1.028049298767531</v>
       </c>
       <c r="W4">
-        <v>0.1016042780748663</v>
+        <v>0.3517490952955368</v>
       </c>
       <c r="X4">
-        <v>0.05334437448743433</v>
+        <v>0.07959923857111041</v>
       </c>
       <c r="Y4">
-        <v>0.04825990358743198</v>
+        <v>0.2721498567244264</v>
       </c>
       <c r="Z4">
-        <v>0.8638497652582158</v>
+        <v>0.6362492133417244</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05334437448743433</v>
+        <v>0.07958992383994333</v>
       </c>
       <c r="AC4">
-        <v>-0.05334437448743433</v>
+        <v>-0.07958992383994333</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="AG4">
-        <v>-32.5</v>
+        <v>-241.799</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.0004290551017200437</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.0002325576040580151</v>
       </c>
       <c r="AJ4">
-        <v>-3.385416666666666</v>
+        <v>37.20557008770583</v>
       </c>
       <c r="AK4">
-        <v>-1.116838487972509</v>
+        <v>-1.256745027312748</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0809</v>
+        <v>0.0414</v>
       </c>
       <c r="E5">
-        <v>-0.0655</v>
+        <v>0.141</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,206 +969,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>182.5</v>
+        <v>266.1</v>
       </c>
       <c r="L5">
-        <v>0.2848891664064939</v>
+        <v>0.3896617367110851</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>261.6</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.09005163511187608</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.9830890642615558</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>261.6</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.09005163511187608</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.9830890642615558</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>855.4</v>
+        <v>782.7</v>
       </c>
       <c r="V5">
-        <v>0.2721170669635756</v>
+        <v>0.2694320137693632</v>
       </c>
       <c r="W5">
-        <v>0.05894512451148219</v>
+        <v>0.08139108093228116</v>
       </c>
       <c r="X5">
-        <v>0.05461235769017948</v>
+        <v>0.08387441405565216</v>
       </c>
       <c r="Y5">
-        <v>0.004332766821302708</v>
+        <v>-0.002483333123370998</v>
       </c>
       <c r="Z5">
-        <v>0.2841302226559035</v>
+        <v>0.2687418834363071</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05391157174600293</v>
+        <v>0.08092041462216697</v>
       </c>
       <c r="AC5">
-        <v>-0.05391157174600293</v>
+        <v>-0.08092041462216697</v>
       </c>
       <c r="AD5">
-        <v>127.1</v>
+        <v>372.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>127.1</v>
+        <v>372.6</v>
       </c>
       <c r="AG5">
-        <v>-728.3</v>
+        <v>-410.1</v>
       </c>
       <c r="AH5">
-        <v>0.03886137100226258</v>
+        <v>0.1136807420063461</v>
       </c>
       <c r="AI5">
-        <v>0.03737575721931424</v>
+        <v>0.1245279235319675</v>
       </c>
       <c r="AJ5">
-        <v>-0.3015485260019874</v>
+        <v>-0.1643753256643553</v>
       </c>
       <c r="AK5">
-        <v>-0.2861464717900362</v>
+        <v>-0.1856160043450711</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Agram banka d.d. (ZGSE:KBZ)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0833</v>
-      </c>
-      <c r="E6">
-        <v>0.294</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>7.98</v>
-      </c>
-      <c r="L6">
-        <v>0.3694444444444445</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>11</v>
-      </c>
-      <c r="V6">
-        <v>0.1713395638629283</v>
-      </c>
-      <c r="W6">
-        <v>0.1216463414634146</v>
-      </c>
-      <c r="X6">
-        <v>0.05959691272139244</v>
-      </c>
-      <c r="Y6">
-        <v>0.0620494287420222</v>
-      </c>
-      <c r="Z6">
-        <v>0.3257918552036199</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05681538993366804</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05681538993366804</v>
-      </c>
-      <c r="AD6">
-        <v>12.8</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>12.8</v>
-      </c>
-      <c r="AG6">
-        <v>1.800000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.1662337662337662</v>
-      </c>
-      <c r="AI6">
-        <v>0.1490104772991851</v>
-      </c>
-      <c r="AJ6">
-        <v>0.02727272727272728</v>
-      </c>
-      <c r="AK6">
-        <v>0.02403204272363152</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/croatia/croatia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.062</v>
+        <v>0.102</v>
       </c>
       <c r="E2">
-        <v>0.172</v>
+        <v>0.22</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>418.22</v>
+        <v>494.81</v>
       </c>
       <c r="L2">
-        <v>0.5216013968570716</v>
+        <v>0.4286667244217275</v>
       </c>
       <c r="M2">
-        <v>264.68</v>
+        <v>261.5798</v>
       </c>
       <c r="N2">
-        <v>0.08297438791184676</v>
+        <v>0.04518176008290872</v>
       </c>
       <c r="O2">
-        <v>0.6328726507579743</v>
+        <v>0.5286469553970211</v>
       </c>
       <c r="P2">
-        <v>264.68</v>
+        <v>260.8258</v>
       </c>
       <c r="Q2">
-        <v>0.08297438791184676</v>
+        <v>0.04505152431125313</v>
       </c>
       <c r="R2">
-        <v>0.6328726507579743</v>
+        <v>0.5271231381742487</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.7540000000000002</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002882485574191891</v>
       </c>
       <c r="U2">
-        <v>1050.8</v>
+        <v>1131.9</v>
       </c>
       <c r="V2">
-        <v>0.3294147151948337</v>
+        <v>0.1955091113222213</v>
       </c>
       <c r="W2">
-        <v>0.1025974025974026</v>
+        <v>0.1521201413427562</v>
       </c>
       <c r="X2">
-        <v>0.07959923857111041</v>
+        <v>0.06787368903144202</v>
       </c>
       <c r="Y2">
-        <v>0.02299816402629219</v>
+        <v>0.08424645231131415</v>
       </c>
       <c r="Z2">
-        <v>0.2937964896852442</v>
+        <v>0.4758232096033598</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07958992383994333</v>
+        <v>0.06787086054297328</v>
       </c>
       <c r="AC2">
-        <v>-0.07958992383994333</v>
+        <v>-0.06787086054297328</v>
       </c>
       <c r="AD2">
-        <v>372.701</v>
+        <v>399.285</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>372.701</v>
+        <v>399.285</v>
       </c>
       <c r="AG2">
-        <v>-678.0989999999999</v>
+        <v>-732.6150000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1046148586383937</v>
+        <v>0.06451751030291082</v>
       </c>
       <c r="AI2">
-        <v>0.1070579648240701</v>
+        <v>0.1072745517633262</v>
       </c>
       <c r="AJ2">
-        <v>-0.2699652560055513</v>
+        <v>-0.1448747598571057</v>
       </c>
       <c r="AK2">
-        <v>-0.2789955651118843</v>
+        <v>-0.282842731310698</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.062</v>
+        <v>0.102</v>
       </c>
       <c r="E3">
-        <v>0.172</v>
+        <v>0.256</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,61 +728,61 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>6.32</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3550561797752809</v>
+        <v>0.3776315789473684</v>
       </c>
       <c r="M3">
-        <v>3.08</v>
+        <v>2.644</v>
       </c>
       <c r="N3">
-        <v>0.06209677419354839</v>
+        <v>0.04278317152103561</v>
       </c>
       <c r="O3">
-        <v>0.4873417721518987</v>
+        <v>0.3070847851335656</v>
       </c>
       <c r="P3">
-        <v>3.08</v>
+        <v>1.89</v>
       </c>
       <c r="Q3">
-        <v>0.06209677419354839</v>
+        <v>0.03058252427184466</v>
       </c>
       <c r="R3">
-        <v>0.4873417721518987</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.7540000000000002</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2851739788199698</v>
       </c>
       <c r="U3">
-        <v>26.2</v>
+        <v>11</v>
       </c>
       <c r="V3">
-        <v>0.5282258064516129</v>
+        <v>0.1779935275080906</v>
       </c>
       <c r="W3">
-        <v>0.1025974025974026</v>
+        <v>0.1521201413427562</v>
       </c>
       <c r="X3">
-        <v>0.07958488326285784</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="Y3">
-        <v>0.02301251933454476</v>
+        <v>0.08425129364628295</v>
       </c>
       <c r="Z3">
-        <v>0.6116838487972509</v>
+        <v>0.8413284132841328</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07958488326285784</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="AC3">
-        <v>-0.07958488326285784</v>
+        <v>-0.06786884769647322</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-26.2</v>
+        <v>-11</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.119658119658119</v>
+        <v>-0.2165354330708661</v>
       </c>
       <c r="AK3">
-        <v>-0.9128919860627178</v>
+        <v>-0.2003642987249545</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0917</v>
+        <v>0.166</v>
       </c>
       <c r="E4">
-        <v>0.982</v>
+        <v>0.22</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,82 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>145.8</v>
+        <v>49.6</v>
       </c>
       <c r="L4">
-        <v>1.442136498516321</v>
+        <v>0.2569948186528497</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>5.6358</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.01346666666666667</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.113625</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>5.6358</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01346666666666667</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.113625</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>241.9</v>
+        <v>176.4</v>
       </c>
       <c r="V4">
-        <v>1.028049298767531</v>
+        <v>0.421505376344086</v>
       </c>
       <c r="W4">
-        <v>0.3517490952955368</v>
+        <v>0.1142330723169047</v>
       </c>
       <c r="X4">
-        <v>0.07959923857111041</v>
+        <v>0.06787368903144202</v>
       </c>
       <c r="Y4">
-        <v>0.2721498567244264</v>
+        <v>0.04635938328546264</v>
       </c>
       <c r="Z4">
-        <v>0.6362492133417244</v>
+        <v>1.003113289431968</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07958992383994333</v>
+        <v>0.06787086054297328</v>
       </c>
       <c r="AC4">
-        <v>-0.07958992383994333</v>
+        <v>-0.06787086054297328</v>
       </c>
       <c r="AD4">
-        <v>0.101</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.101</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AG4">
-        <v>-241.799</v>
+        <v>-176.315</v>
       </c>
       <c r="AH4">
-        <v>0.0004290551017200437</v>
+        <v>0.0002030650883333135</v>
       </c>
       <c r="AI4">
-        <v>0.0002325576040580151</v>
+        <v>0.0001529368370862833</v>
       </c>
       <c r="AJ4">
-        <v>37.20557008770583</v>
+        <v>-0.7280178376034849</v>
       </c>
       <c r="AK4">
-        <v>-1.256745027312748</v>
+        <v>-0.4647389854633155</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0414</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="E5">
-        <v>0.141</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>266.1</v>
+        <v>436.6</v>
       </c>
       <c r="L5">
-        <v>0.3896617367110851</v>
+        <v>0.465210442194992</v>
       </c>
       <c r="M5">
-        <v>261.6</v>
+        <v>253.3</v>
       </c>
       <c r="N5">
-        <v>0.09005163511187608</v>
+        <v>0.04770963610336774</v>
       </c>
       <c r="O5">
-        <v>0.9830890642615558</v>
+        <v>0.5801649106733853</v>
       </c>
       <c r="P5">
-        <v>261.6</v>
+        <v>253.3</v>
       </c>
       <c r="Q5">
-        <v>0.09005163511187608</v>
+        <v>0.04770963610336774</v>
       </c>
       <c r="R5">
-        <v>0.9830890642615558</v>
+        <v>0.5801649106733853</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -999,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>782.7</v>
+        <v>944.5</v>
       </c>
       <c r="V5">
-        <v>0.2694320137693632</v>
+        <v>0.1778987418066752</v>
       </c>
       <c r="W5">
-        <v>0.08139108093228116</v>
+        <v>0.1668641314733423</v>
       </c>
       <c r="X5">
-        <v>0.08387441405565216</v>
+        <v>0.06966111637732048</v>
       </c>
       <c r="Y5">
-        <v>-0.002483333123370998</v>
+        <v>0.09720301509602178</v>
       </c>
       <c r="Z5">
-        <v>0.2687418834363071</v>
+        <v>0.4253535170413344</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08092041462216697</v>
+        <v>0.0690483731892521</v>
       </c>
       <c r="AC5">
-        <v>-0.08092041462216697</v>
+        <v>-0.0690483731892521</v>
       </c>
       <c r="AD5">
-        <v>372.6</v>
+        <v>399.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>372.6</v>
+        <v>399.2</v>
       </c>
       <c r="AG5">
-        <v>-410.1</v>
+        <v>-545.3</v>
       </c>
       <c r="AH5">
-        <v>0.1136807420063461</v>
+        <v>0.06993202999089063</v>
       </c>
       <c r="AI5">
-        <v>0.1245279235319675</v>
+        <v>0.1287575796671397</v>
       </c>
       <c r="AJ5">
-        <v>-0.1643753256643553</v>
+        <v>-0.1144650391485967</v>
       </c>
       <c r="AK5">
-        <v>-0.1856160043450711</v>
+        <v>-0.2529338095458973</v>
       </c>
       <c r="AL5">
         <v>0</v>
